--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2382-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2382-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA467E0B-5952-4E71-9CC3-8F9343F449B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D24B507-D592-4447-9293-992B7745C461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C985F626-47B8-4FED-9740-E81F026D735F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{39BBB775-21A9-4C52-96A6-9A90779D1BFC}"/>
   </bookViews>
   <sheets>
     <sheet name="2382-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1529,30 +1529,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3FAB2FB-C094-4EAA-ACB2-252468B493AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42EBEFED-7AEB-4D8A-BDBD-1F39C94E3973}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1742,7 +1742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2020</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2019</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2018</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2017</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2016</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2015</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2014</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2013</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2012</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2011</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2010</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2009</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2008</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2007</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2006</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2005</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2004</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2003</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2002</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2001</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2000</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1999</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1998</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1997</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1996</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1995</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1994</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1993</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1992</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
         <v>63</v>
       </c>
